--- a/pacjenci/GRZEGORZ KOSOWSKI.xlsx
+++ b/pacjenci/GRZEGORZ KOSOWSKI.xlsx
@@ -485,7 +485,7 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -529,12 +529,12 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Do oceny</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -542,17 +542,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
+          <t>4 - utrzymujący się wychwyt patologiczny</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
+          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
         </is>
       </c>
     </row>
@@ -573,12 +573,12 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Do oceny</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -586,17 +586,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
+          <t>4 - utrzymujący się wychwyt patologiczny</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
+          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
         </is>
       </c>
     </row>

--- a/pacjenci/GRZEGORZ KOSOWSKI.xlsx
+++ b/pacjenci/GRZEGORZ KOSOWSKI.xlsx
@@ -413,191 +413,143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>15.06.2021</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy guzkowy [grudkowy]. Ocena zaawansowania klinicznego .  OPIS: Ibraheem Al Maraih</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 56 min od podania 18F-FDG. Glikemia: 96mmol/l</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Aktywne i pobudzone metabolicznie węzły chłonne: -  2A po stronie lewej o wielkości  8x11mm,  SUV max 6,0 -  2A po stronie prawej o wielkości  6x8m,  SUV max 5,0 - 1B po stronie lewej o wielkości 9x15mm,  SUV max 7,0 - 1B po stronie prawej o wielkości 10x14mm,  SUV max 5,5 - 2B po stronie lewej o wielkości 5x6mm,  SUV max 3,8 - 2B po stronie prawej o wielkości 6x7mm,  SUV max 3,7 - 3 po stronie lewej o wielkości 6x7mm,  SUV max 4,4 - 3 po stronie prawej o wielkości 5x7,5mm,  SUV max 3,4 Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Pobudzone metabolicznie węzły chłonne pachowe prawe wielkości 22mm, SUV max 1,3 [im fuz 166] Wnęka płuca lewego SUV max do 3,0, wnęka płuca prawego, SUV max do 3,3.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobny uwapniony guzek w segmencie 3 płuca prawego [Im 299] Zmiany włókniste w nadprzeponowych segmentach obu płuc.  Brzuch i miednica: Aktywne i pobudzone metabolicznie węzły chłonne: - okołoaortalne po stronie lewej o wielkości 24x26mm , SUV max do 5,1 [im fuz 209] - okołoaortalne po stronie prawej o wielkości 19x28mm , SUV max do 6,6 [im fuz 205] - liczne spakietowane i pojedyncze pobudzone i aktywne metabolicznie węzły chłonne krezkowe wielkości do 36x23x42mm, SUV max do 8,8 - pojedyncze aktywne metabolicznie węzły chłonne przykręgosłupowe po stronie prawej wielkości do 16x13 mm, SUV max do 4,6 - biodrowe zewnętrzne po stronie prawej wielkości 18x18mm, SUV max 7,6 - pachwinowe prawej wielkości 13x13mm, SUV max 5,0 - pachwinowe lewej wielkości 10x13mm, SUV max 3,5 Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo widoczne drobne guzki Schmorla. Wyspa kostna w głowie kości udowej prawej.  Wartości referencyjne: MBPS SUVmax 2,1 Prawy płat wątroby SUVmax do 3,2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywne metabolicznie węzły chłonne po obu stronach przepony. Poza tym jak powyżej</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>21.10.2021</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy grudkowy. Ocena odpowiedzi po 3 cyklach ChTh.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 59 min od podania 18F-FDG. Glikemia: 73 mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Tarczyca powiększona, schodzi nisko do śródpiersia przedniego, z drobnymi zwapnieniami, o niejednorodnym cieniowaniu w przeglądowym badaniu TK - do kontroli w USG.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne obwodowe zmiany włókniste w płatach górnych obu płuc. Drobny uwapniony guzek w segmencie 3 płuca prawego. Niewielkie zmiany miąższowo-włókniste w segm. 4 płuca lewego. Niewielkie zmiany włókniste w nadprzeponowych segmentach obu płuc.  Brzuch i miednica: Rozlanie wzmożony metabolizm FDG w żołądku SUV max  do 4,9 - w pierwszej kolejności o charakterze odczynowym. Rozlanie i odcinkowo wzmożony metabolizm FDG w jelitach - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne okołoaortalne obustronnie, wielkości do 13 mm [Im CT 476].  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Nieznaczna prawowypukła skolioza kręgosłupa piersiowego. Wielopoziomowo drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Drobne wyspy kostne w trzonach kręgowych. Niejednorodna przebudowa struktury kostnej trzonu i nieco przyległej części talerza prawej kości biodrowej. Wyspa kostna w głowie prawej kości udowej.  Wartości referencyjne: MBPS SUVmax 2,1; Prawy płat wątroby SUVmax do 3,5.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej. Poza tym jak powyżej</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>4.9</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>10.02.2022</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy grudkowy. Ocena remisji choroby po zakończeniu immunochemioterapii I rzutu.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 59 min od podania 18F-FDG. Glikemia: 97 mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Asymetrycznie wzmożony metabolizm FDG w topografii lewego migdałka gardłowego SUV max do 6,0- do kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Tarczyca powiększona, schodzi nisko do śródpiersia przedniego, z drobnymi zwapnieniami, o niejednorodnym cieniowaniu w przeglądowym badaniu TK - do kontroli w USG.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne obwodowe zmiany włókniste w płatach górnych obu płuc. Drobny uwapniony guzek w segmencie 3 płuca prawego. Niewielkie zmiany miąższowo-włókniste w segm. 4 płuca lewego oraz 10 płuca prawego. Niewielkie zmiany włókniste w nadprzeponowych segmentach obu płuc.  Brzuch i miednica: Rozlanie wzmożony metabolizm FDG w dnie żołądka SUV max  do 5,2 - w pierwszej kolejności o charakterze odczynowym. Rozlanie i odcinkowo wzmożony metabolizm FDG w jelitach - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne okołoaortalne obustronnie, wielkości do 13x11 mm.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Nieznaczna prawowypukła skolioza kręgosłupa piersiowego. Wielopoziomowo drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Drobne wyspy kostne w trzonach kręgowych. Niejednorodna przebudowa struktury kostnej trzonu i nieco przyległej części talerza prawej kości biodrowej.  Wyspa kostna w głowie prawej kości udowej wielkości 10x5mm oraz druga drobna.  Inne: Wzmożony metabolizm FDG w mięśniach ramienia prawego SUV max 5,1- zmiany odczynowo-przeciążeniowe.  Wartości referencyjne: MBPS SUVmax 1,9; Prawy płat wątroby SUVmax do 3,8.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej.  Poza tym jak powyżej</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>6</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/GRZEGORZ KOSOWSKI.xlsx
+++ b/pacjenci/GRZEGORZ KOSOWSKI.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 56 min od podania 18F-FDG. Glikemia: 96mmol/l</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Aktywne i pobudzone metabolicznie węzły chłonne: -  2A po stronie lewej o wielkości  8x11mm,  SUV max 6,0 -  2A po stronie prawej o wielkości  6x8m,  SUV max 5,0 - 1B po stronie lewej o wielkości 9x15mm,  SUV max 7,0 - 1B po stronie prawej o wielkości 10x14mm,  SUV max 5,5 - 2B po stronie lewej o wielkości 5x6mm,  SUV max 3,8 - 2B po stronie prawej o wielkości 6x7mm,  SUV max 3,7 - 3 po stronie lewej o wielkości 6x7mm,  SUV max 4,4 - 3 po stronie prawej o wielkości 5x7,5mm,  SUV max 3,4 Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Pobudzone metabolicznie węzły chłonne pachowe prawe wielkości 22mm, SUV max 1,3 [im fuz 166] Wnęka płuca lewego SUV max do 3,0, wnęka płuca prawego, SUV max do 3,3.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobny uwapniony guzek w segmencie 3 płuca prawego [Im 299] Zmiany włókniste w nadprzeponowych segmentach obu płuc.  Brzuch i miednica: Aktywne i pobudzone metabolicznie węzły chłonne: - okołoaortalne po stronie lewej o wielkości 24x26mm , SUV max do 5,1 [im fuz 209] - okołoaortalne po stronie prawej o wielkości 19x28mm , SUV max do 6,6 [im fuz 205] - liczne spakietowane i pojedyncze pobudzone i aktywne metabolicznie węzły chłonne krezkowe wielkości do 36x23x42mm, SUV max do 8,8 - pojedyncze aktywne metabolicznie węzły chłonne przykręgosłupowe po stronie prawej wielkości do 16x13 mm, SUV max do 4,6 - biodrowe zewnętrzne po stronie prawej wielkości 18x18mm, SUV max 7,6 - pachwinowe prawej wielkości 13x13mm, SUV max 5,0 - pachwinowe lewej wielkości 10x13mm, SUV max 3,5 Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo widoczne drobne guzki Schmorla. Wyspa kostna w głowie kości udowej prawej.  Wartości referencyjne: MBPS SUVmax 2,1 Prawy płat wątroby SUVmax do 3,2</t>
+          <t>96</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Aktywne i pobudzone metabolicznie węzły chłonne: -  2A po stronie lewej o wielkości  8x11mm,  SUV max 6,0 -  2A po stronie prawej o wielkości  6x8m,  SUV max 5,0 - 1B po stronie lewej o wielkości 9x15mm,  SUV max 7,0 - 1B po stronie prawej o wielkości 10x14mm,  SUV max 5,5 - 2B po stronie lewej o wielkości 5x6mm,  SUV max 3,8 - 2B po stronie prawej o wielkości 6x7mm,  SUV max 3,7 - 3 po stronie lewej o wielkości 6x7mm,  SUV max 4,4 - 3 po stronie prawej o wielkości 5x7,5mm,  SUV max 3,4 Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Pobudzone metabolicznie węzły chłonne pachowe prawe wielkości 22mm, SUV max 1,3 [im fuz 166] Wnęka płuca lewego SUV max do 3,0, wnęka płuca prawego, SUV max do 3,3.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobny uwapniony guzek w segmencie 3 płuca prawego [Im 299] Zmiany włókniste w nadprzeponowych segmentach obu płuc.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Aktywne i pobudzone metabolicznie węzły chłonne: - okołoaortalne po stronie lewej o wielkości 24x26mm , SUV max do 5,1 [im fuz 209] - okołoaortalne po stronie prawej o wielkości 19x28mm , SUV max do 6,6 [im fuz 205] - liczne spakietowane i pojedyncze pobudzone i aktywne metabolicznie węzły chłonne krezkowe wielkości do 36x23x42mm, SUV max do 8,8 - pojedyncze aktywne metabolicznie węzły chłonne przykręgosłupowe po stronie prawej wielkości do 16x13 mm, SUV max do 4,6 - biodrowe zewnętrzne po stronie prawej wielkości 18x18mm, SUV max 7,6 - pachwinowe prawej wielkości 13x13mm, SUV max 5,0 - pachwinowe lewej wielkości 10x13mm, SUV max 3,5 Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo widoczne drobne guzki Schmorla. Wyspa kostna w głowie kości udowej prawej.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywne metabolicznie węzły chłonne po obu stronach przepony. Poza tym jak powyżej</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>8.800000000000001</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 59 min od podania 18F-FDG. Glikemia: 73 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Tarczyca powiększona, schodzi nisko do śródpiersia przedniego, z drobnymi zwapnieniami, o niejednorodnym cieniowaniu w przeglądowym badaniu TK - do kontroli w USG.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne obwodowe zmiany włókniste w płatach górnych obu płuc. Drobny uwapniony guzek w segmencie 3 płuca prawego. Niewielkie zmiany miąższowo-włókniste w segm. 4 płuca lewego. Niewielkie zmiany włókniste w nadprzeponowych segmentach obu płuc.  Brzuch i miednica: Rozlanie wzmożony metabolizm FDG w żołądku SUV max  do 4,9 - w pierwszej kolejności o charakterze odczynowym. Rozlanie i odcinkowo wzmożony metabolizm FDG w jelitach - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne okołoaortalne obustronnie, wielkości do 13 mm [Im CT 476].  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Nieznaczna prawowypukła skolioza kręgosłupa piersiowego. Wielopoziomowo drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Drobne wyspy kostne w trzonach kręgowych. Niejednorodna przebudowa struktury kostnej trzonu i nieco przyległej części talerza prawej kości biodrowej. Wyspa kostna w głowie prawej kości udowej.  Wartości referencyjne: MBPS SUVmax 2,1; Prawy płat wątroby SUVmax do 3,5.</t>
+          <t>73</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Tarczyca powiększona, schodzi nisko do śródpiersia przedniego, z drobnymi zwapnieniami, o niejednorodnym cieniowaniu w przeglądowym badaniu TK - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne obwodowe zmiany włókniste w płatach górnych obu płuc. Drobny uwapniony guzek w segmencie 3 płuca prawego. Niewielkie zmiany miąższowo-włókniste w segm. 4 płuca lewego. Niewielkie zmiany włókniste w nadprzeponowych segmentach obu płuc.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Rozlanie wzmożony metabolizm FDG w żołądku SUV max  do 4,9 - w pierwszej kolejności o charakterze odczynowym. Rozlanie i odcinkowo wzmożony metabolizm FDG w jelitach - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne okołoaortalne obustronnie, wielkości do 13 mm [Im CT 476].</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Nieznaczna prawowypukła skolioza kręgosłupa piersiowego. Wielopoziomowo drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Drobne wyspy kostne w trzonach kręgowych. Niejednorodna przebudowa struktury kostnej trzonu i nieco przyległej części talerza prawej kości biodrowej. Wyspa kostna w głowie prawej kości udowej.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej. Poza tym jak powyżej</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>4.9</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 59 min od podania 18F-FDG. Glikemia: 97 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Asymetrycznie wzmożony metabolizm FDG w topografii lewego migdałka gardłowego SUV max do 6,0- do kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Tarczyca powiększona, schodzi nisko do śródpiersia przedniego, z drobnymi zwapnieniami, o niejednorodnym cieniowaniu w przeglądowym badaniu TK - do kontroli w USG.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne obwodowe zmiany włókniste w płatach górnych obu płuc. Drobny uwapniony guzek w segmencie 3 płuca prawego. Niewielkie zmiany miąższowo-włókniste w segm. 4 płuca lewego oraz 10 płuca prawego. Niewielkie zmiany włókniste w nadprzeponowych segmentach obu płuc.  Brzuch i miednica: Rozlanie wzmożony metabolizm FDG w dnie żołądka SUV max  do 5,2 - w pierwszej kolejności o charakterze odczynowym. Rozlanie i odcinkowo wzmożony metabolizm FDG w jelitach - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne okołoaortalne obustronnie, wielkości do 13x11 mm.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Nieznaczna prawowypukła skolioza kręgosłupa piersiowego. Wielopoziomowo drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Drobne wyspy kostne w trzonach kręgowych. Niejednorodna przebudowa struktury kostnej trzonu i nieco przyległej części talerza prawej kości biodrowej.  Wyspa kostna w głowie prawej kości udowej wielkości 10x5mm oraz druga drobna.  Inne: Wzmożony metabolizm FDG w mięśniach ramienia prawego SUV max 5,1- zmiany odczynowo-przeciążeniowe.  Wartości referencyjne: MBPS SUVmax 1,9; Prawy płat wątroby SUVmax do 3,8.</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Asymetrycznie wzmożony metabolizm FDG w topografii lewego migdałka gardłowego SUV max do 6,0- do kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Tarczyca powiększona, schodzi nisko do śródpiersia przedniego, z drobnymi zwapnieniami, o niejednorodnym cieniowaniu w przeglądowym badaniu TK - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne obwodowe zmiany włókniste w płatach górnych obu płuc. Drobny uwapniony guzek w segmencie 3 płuca prawego. Niewielkie zmiany miąższowo-włókniste w segm. 4 płuca lewego oraz 10 płuca prawego. Niewielkie zmiany włókniste w nadprzeponowych segmentach obu płuc.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Rozlanie wzmożony metabolizm FDG w dnie żołądka SUV max  do 5,2 - w pierwszej kolejności o charakterze odczynowym. Rozlanie i odcinkowo wzmożony metabolizm FDG w jelitach - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne okołoaortalne obustronnie, wielkości do 13x11 mm.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Nieznaczna prawowypukła skolioza kręgosłupa piersiowego. Wielopoziomowo drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Drobne wyspy kostne w trzonach kręgowych. Niejednorodna przebudowa struktury kostnej trzonu i nieco przyległej części talerza prawej kości biodrowej.  Wyspa kostna w głowie prawej kości udowej wielkości 10x5mm oraz druga drobna.  Inne: Wzmożony metabolizm FDG w mięśniach ramienia prawego SUV max 5,1- zmiany odczynowo-przeciążeniowe.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej.  Poza tym jak powyżej</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>6</v>
       </c>
     </row>
